--- a/tables/Datas/monster.xlsx
+++ b/tables/Datas/monster.xlsx
@@ -1521,7 +1521,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>10</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:31">
@@ -1538,7 +1538,7 @@
         <v>10001</v>
       </c>
       <c r="H7">
-        <v>380</v>
+        <v>330</v>
       </c>
       <c r="I7">
         <v>300</v>
@@ -1562,7 +1562,7 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>10</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:31">
@@ -1603,7 +1603,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>10</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:31">
@@ -1620,10 +1620,10 @@
         <v>10001</v>
       </c>
       <c r="H9">
-        <v>380</v>
+        <v>499</v>
       </c>
       <c r="I9">
-        <v>336</v>
+        <v>247</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1644,7 +1644,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>10</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:31">
@@ -1685,7 +1685,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>10</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:31">
@@ -1726,7 +1726,7 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>10</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:31">
@@ -1767,7 +1767,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>10</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:31">
@@ -1808,7 +1808,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>10</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:31">
@@ -1849,7 +1849,7 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>10</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:31">
@@ -1890,7 +1890,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>10</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/tables/Datas/monster.xlsx
+++ b/tables/Datas/monster.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="57">
   <si>
     <t>##var</t>
   </si>
@@ -114,6 +114,9 @@
     <t>speed_percent</t>
   </si>
   <si>
+    <t>drop_id</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -200,6 +203,9 @@
   </si>
   <si>
     <t>速度百分比加成</t>
+  </si>
+  <si>
+    <t>掉落</t>
   </si>
   <si>
     <t>史莱姆1</t>
@@ -1190,6 +1196,7 @@
   <cols>
     <col min="1" max="2" width="9.225" customWidth="1"/>
     <col min="3" max="23" width="23" customWidth="1"/>
+    <col min="24" max="24" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:31">
@@ -1260,7 +1267,9 @@
       <c r="W1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="X1"/>
+      <c r="X1" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="Y1"/>
       <c r="Z1"/>
       <c r="AA1"/>
@@ -1297,7 +1306,7 @@
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
       <c r="W2" s="4"/>
-      <c r="X2"/>
+      <c r="X2" s="4"/>
       <c r="Y2"/>
       <c r="Z2"/>
       <c r="AA2"/>
@@ -1308,73 +1317,75 @@
     </row>
     <row r="3" s="2" customFormat="1" spans="1:31">
       <c r="A3" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>24</v>
-      </c>
       <c r="G3" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="X3"/>
+        <v>28</v>
+      </c>
+      <c r="X3" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="Y3"/>
       <c r="Z3"/>
       <c r="AA3"/>
@@ -1385,10 +1396,10 @@
     </row>
     <row r="4" s="2" customFormat="1" spans="1:31">
       <c r="A4" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
@@ -1411,7 +1422,7 @@
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
       <c r="W4" s="6"/>
-      <c r="X4"/>
+      <c r="X4" s="6"/>
       <c r="Y4"/>
       <c r="Z4"/>
       <c r="AA4"/>
@@ -1422,15 +1433,15 @@
     </row>
     <row r="5" s="1" customFormat="1" spans="1:31">
       <c r="A5" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
@@ -1439,42 +1450,44 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="X5"/>
+        <v>45</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="Y5"/>
       <c r="Z5"/>
       <c r="AA5"/>
@@ -1488,7 +1501,7 @@
         <v>10001</v>
       </c>
       <c r="E6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1529,7 +1542,7 @@
         <v>10002</v>
       </c>
       <c r="E7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F7">
         <v>2</v>
@@ -1570,7 +1583,7 @@
         <v>10003</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F8">
         <v>3</v>
@@ -1611,7 +1624,7 @@
         <v>10004</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F9">
         <v>4</v>
@@ -1652,7 +1665,7 @@
         <v>10005</v>
       </c>
       <c r="E10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -1693,7 +1706,7 @@
         <v>10006</v>
       </c>
       <c r="E11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F11">
         <v>6</v>
@@ -1734,7 +1747,7 @@
         <v>10007</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F12">
         <v>7</v>
@@ -1775,7 +1788,7 @@
         <v>10008</v>
       </c>
       <c r="E13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F13">
         <v>8</v>
@@ -1816,7 +1829,7 @@
         <v>10009</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F14">
         <v>9</v>
@@ -1857,7 +1870,7 @@
         <v>10010</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F15">
         <v>10</v>

--- a/tables/Datas/monster.xlsx
+++ b/tables/Datas/monster.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
   <si>
     <t>##var</t>
   </si>
@@ -66,18 +66,6 @@
     <t>map_id</t>
   </si>
   <si>
-    <t>spawn_x</t>
-  </si>
-  <si>
-    <t>spawn_y</t>
-  </si>
-  <si>
-    <t>spawn_z</t>
-  </si>
-  <si>
-    <t>respawn_time</t>
-  </si>
-  <si>
     <t>hp</t>
   </si>
   <si>
@@ -93,12 +81,6 @@
     <t>speed</t>
   </si>
   <si>
-    <t>hp_recover</t>
-  </si>
-  <si>
-    <t>mp_recover</t>
-  </si>
-  <si>
     <t>attack_percent</t>
   </si>
   <si>
@@ -127,9 +109,6 @@
   </si>
   <si>
     <t>string</t>
-  </si>
-  <si>
-    <t>float</t>
   </si>
   <si>
     <t>double</t>
@@ -182,12 +161,6 @@
   </si>
   <si>
     <t>速度</t>
-  </si>
-  <si>
-    <t>生命回复</t>
-  </si>
-  <si>
-    <t>法力回复</t>
   </si>
   <si>
     <t>攻击力百分比加成</t>
@@ -1191,15 +1164,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE15"/>
+  <dimension ref="A1:Y15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="9.225" customWidth="1"/>
-    <col min="3" max="23" width="23" customWidth="1"/>
-    <col min="24" max="24" width="15" customWidth="1"/>
+    <col min="3" max="17" width="23" customWidth="1"/>
+    <col min="18" max="18" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:31">
+    <row r="1" s="1" customFormat="1" spans="1:25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1252,33 +1225,15 @@
       <c r="R1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>22</v>
-      </c>
+      <c r="S1"/>
+      <c r="T1"/>
+      <c r="U1"/>
+      <c r="V1"/>
+      <c r="W1"/>
+      <c r="X1"/>
       <c r="Y1"/>
-      <c r="Z1"/>
-      <c r="AA1"/>
-      <c r="AB1"/>
-      <c r="AC1"/>
-      <c r="AD1"/>
-      <c r="AE1"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:31">
+    <row r="2" s="1" customFormat="1" spans="1:25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1301,105 +1256,81 @@
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
       <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2"/>
-      <c r="AB2"/>
-      <c r="AC2"/>
-      <c r="AD2"/>
-      <c r="AE2"/>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:31">
+    <row r="3" s="2" customFormat="1" spans="1:25">
       <c r="A3" s="5" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="S3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="T3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="U3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="V3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="W3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="X3" s="6" t="s">
-        <v>25</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="S3"/>
+      <c r="T3"/>
+      <c r="U3"/>
+      <c r="V3"/>
+      <c r="W3"/>
+      <c r="X3"/>
       <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3"/>
-      <c r="AB3"/>
-      <c r="AC3"/>
-      <c r="AD3"/>
-      <c r="AE3"/>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:31">
+    <row r="4" s="2" customFormat="1" spans="1:25">
       <c r="A4" s="5" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
@@ -1417,91 +1348,75 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
+      <c r="S4"/>
+      <c r="T4"/>
+      <c r="U4"/>
+      <c r="V4"/>
+      <c r="W4"/>
+      <c r="X4"/>
       <c r="Y4"/>
-      <c r="Z4"/>
-      <c r="AA4"/>
-      <c r="AB4"/>
-      <c r="AC4"/>
-      <c r="AD4"/>
-      <c r="AE4"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:31">
+    <row r="5" s="1" customFormat="1" spans="1:25">
       <c r="A5" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="4" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
+      <c r="H5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>30</v>
+      </c>
       <c r="L5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="P5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="Q5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="R5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="P5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="R5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="S5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="T5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="U5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="V5" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="W5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" s="4" t="s">
-        <v>46</v>
-      </c>
+      <c r="S5"/>
+      <c r="T5"/>
+      <c r="U5"/>
+      <c r="V5"/>
+      <c r="W5"/>
+      <c r="X5"/>
       <c r="Y5"/>
-      <c r="Z5"/>
-      <c r="AA5"/>
-      <c r="AB5"/>
-      <c r="AC5"/>
-      <c r="AD5"/>
-      <c r="AE5"/>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:25">
       <c r="C6">
         <v>10001</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1510,39 +1425,27 @@
         <v>10001</v>
       </c>
       <c r="H6">
-        <v>401</v>
+        <v>100</v>
       </c>
       <c r="I6">
-        <v>333</v>
+        <v>100</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K6">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="L6">
-        <v>100</v>
-      </c>
-      <c r="M6">
-        <v>100</v>
-      </c>
-      <c r="N6">
-        <v>100</v>
-      </c>
-      <c r="O6">
-        <v>100</v>
-      </c>
-      <c r="P6">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:25">
       <c r="C7">
         <v>10002</v>
       </c>
       <c r="E7" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F7">
         <v>2</v>
@@ -1551,39 +1454,27 @@
         <v>10001</v>
       </c>
       <c r="H7">
-        <v>330</v>
+        <v>100</v>
       </c>
       <c r="I7">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K7">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="L7">
-        <v>100</v>
-      </c>
-      <c r="M7">
-        <v>100</v>
-      </c>
-      <c r="N7">
-        <v>100</v>
-      </c>
-      <c r="O7">
-        <v>100</v>
-      </c>
-      <c r="P7">
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:25">
       <c r="C8">
         <v>10003</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F8">
         <v>3</v>
@@ -1592,39 +1483,27 @@
         <v>10001</v>
       </c>
       <c r="H8">
-        <v>380</v>
+        <v>100</v>
       </c>
       <c r="I8">
-        <v>319</v>
+        <v>100</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K8">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="L8">
-        <v>100</v>
-      </c>
-      <c r="M8">
-        <v>100</v>
-      </c>
-      <c r="N8">
-        <v>100</v>
-      </c>
-      <c r="O8">
-        <v>100</v>
-      </c>
-      <c r="P8">
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:25">
       <c r="C9">
         <v>10004</v>
       </c>
       <c r="E9" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F9">
         <v>4</v>
@@ -1633,39 +1512,27 @@
         <v>10001</v>
       </c>
       <c r="H9">
-        <v>499</v>
+        <v>100</v>
       </c>
       <c r="I9">
-        <v>247</v>
+        <v>100</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="L9">
-        <v>100</v>
-      </c>
-      <c r="M9">
-        <v>100</v>
-      </c>
-      <c r="N9">
-        <v>100</v>
-      </c>
-      <c r="O9">
-        <v>100</v>
-      </c>
-      <c r="P9">
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:25">
       <c r="C10">
         <v>10005</v>
       </c>
       <c r="E10" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -1674,39 +1541,27 @@
         <v>10001</v>
       </c>
       <c r="H10">
-        <v>456</v>
+        <v>100</v>
       </c>
       <c r="I10">
-        <v>486</v>
+        <v>100</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="L10">
-        <v>100</v>
-      </c>
-      <c r="M10">
-        <v>100</v>
-      </c>
-      <c r="N10">
-        <v>100</v>
-      </c>
-      <c r="O10">
-        <v>100</v>
-      </c>
-      <c r="P10">
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:25">
       <c r="C11">
         <v>10006</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F11">
         <v>6</v>
@@ -1715,39 +1570,27 @@
         <v>10001</v>
       </c>
       <c r="H11">
-        <v>492</v>
+        <v>100</v>
       </c>
       <c r="I11">
-        <v>461</v>
+        <v>100</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K11">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="L11">
-        <v>100</v>
-      </c>
-      <c r="M11">
-        <v>100</v>
-      </c>
-      <c r="N11">
-        <v>100</v>
-      </c>
-      <c r="O11">
-        <v>100</v>
-      </c>
-      <c r="P11">
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:25">
       <c r="C12">
         <v>10007</v>
       </c>
       <c r="E12" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F12">
         <v>7</v>
@@ -1756,39 +1599,27 @@
         <v>10001</v>
       </c>
       <c r="H12">
-        <v>604</v>
+        <v>100</v>
       </c>
       <c r="I12">
-        <v>428</v>
+        <v>100</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K12">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="L12">
-        <v>100</v>
-      </c>
-      <c r="M12">
-        <v>100</v>
-      </c>
-      <c r="N12">
-        <v>100</v>
-      </c>
-      <c r="O12">
-        <v>100</v>
-      </c>
-      <c r="P12">
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:25">
       <c r="C13">
         <v>10008</v>
       </c>
       <c r="E13" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F13">
         <v>8</v>
@@ -1797,39 +1628,27 @@
         <v>10001</v>
       </c>
       <c r="H13">
-        <v>353</v>
+        <v>100</v>
       </c>
       <c r="I13">
-        <v>373</v>
+        <v>100</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K13">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="L13">
-        <v>100</v>
-      </c>
-      <c r="M13">
-        <v>100</v>
-      </c>
-      <c r="N13">
-        <v>100</v>
-      </c>
-      <c r="O13">
-        <v>100</v>
-      </c>
-      <c r="P13">
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" spans="1:25">
       <c r="C14">
         <v>10009</v>
       </c>
       <c r="E14" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F14">
         <v>9</v>
@@ -1838,39 +1657,27 @@
         <v>10001</v>
       </c>
       <c r="H14">
-        <v>345</v>
+        <v>100</v>
       </c>
       <c r="I14">
-        <v>255</v>
+        <v>100</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K14">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="L14">
-        <v>100</v>
-      </c>
-      <c r="M14">
-        <v>100</v>
-      </c>
-      <c r="N14">
-        <v>100</v>
-      </c>
-      <c r="O14">
-        <v>100</v>
-      </c>
-      <c r="P14">
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" spans="1:25">
       <c r="C15">
         <v>10010</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F15">
         <v>10</v>
@@ -1879,30 +1686,18 @@
         <v>10001</v>
       </c>
       <c r="H15">
-        <v>358</v>
+        <v>100</v>
       </c>
       <c r="I15">
-        <v>153</v>
+        <v>100</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="L15">
-        <v>100</v>
-      </c>
-      <c r="M15">
-        <v>100</v>
-      </c>
-      <c r="N15">
-        <v>100</v>
-      </c>
-      <c r="O15">
-        <v>100</v>
-      </c>
-      <c r="P15">
         <v>60</v>
       </c>
     </row>
